--- a/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
+++ b/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
@@ -10,6 +10,8 @@
     <sheet name="response_time" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="input_tokens" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="llm_calls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="fallback" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="yaml_validity" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -827,4 +829,270 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arch_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_responses</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_runs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fallback_observed_n</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fallback_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>non_fallback_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fallback_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>104</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>104</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2" t="n">
+        <v>91</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>104</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>92</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>104</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>104</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>102</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arch_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_responses</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_runs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>yaml_applicable_n</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>yaml_valid_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>yaml_invalid_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>yaml_missing_n</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>yaml_valid_rate_on_applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>104</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E2" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3" t="n">
+        <v>78</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9069767441860465</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>104</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>92</v>
+      </c>
+      <c r="E4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
+++ b/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
@@ -10,8 +10,9 @@
     <sheet name="response_time" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="input_tokens" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="llm_calls" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="fallback" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="yaml_validity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="code_lines" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="fallback" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="yaml_validity" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -837,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,22 +859,27 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>fallback_observed_n</t>
+          <t>code_lines_avg</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>fallback_count</t>
+          <t>code_lines_std</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>non_fallback_count</t>
+          <t>code_lines_p25</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>fallback_rate</t>
+          <t>code_lines_median</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>code_lines_p75</t>
         </is>
       </c>
     </row>
@@ -890,16 +896,19 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>260</v>
+        <v>20.64230769230769</v>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>20.71443406028218</v>
       </c>
       <c r="F2" t="n">
-        <v>232</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1076923076923077</v>
+        <v>11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -915,16 +924,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>260</v>
+        <v>21.44615384615384</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>21.89570277067626</v>
       </c>
       <c r="F3" t="n">
-        <v>233</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1038461538461539</v>
+        <v>6.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -940,16 +952,19 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>260</v>
+        <v>22.71153846153846</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>20.90310107830019</v>
       </c>
       <c r="F4" t="n">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04230769230769231</v>
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -963,6 +978,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arch_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_responses</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_runs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fallback_observed_n</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fallback_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>non_fallback_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fallback_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>260</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>260</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2" t="n">
+        <v>232</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1076923076923077</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>260</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>260</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F3" t="n">
+        <v>233</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1038461538461539</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>260</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>260</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>249</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.04230769230769231</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
+++ b/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
@@ -476,19 +476,19 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>26.28015593076923</v>
+        <v>29.15273405769231</v>
       </c>
       <c r="E2" t="n">
-        <v>19.55154592377211</v>
+        <v>18.68367103489186</v>
       </c>
       <c r="F2" t="n">
-        <v>13.9687355</v>
+        <v>17.14912675</v>
       </c>
       <c r="G2" t="n">
-        <v>19.1882605</v>
+        <v>21.8696485</v>
       </c>
       <c r="H2" t="n">
-        <v>30.92796825</v>
+        <v>33.2611755</v>
       </c>
     </row>
     <row r="3">
@@ -504,19 +504,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16.53244329615385</v>
+        <v>18.18594827692308</v>
       </c>
       <c r="E3" t="n">
-        <v>11.56608063599925</v>
+        <v>11.86179085453731</v>
       </c>
       <c r="F3" t="n">
-        <v>9.437467249999999</v>
+        <v>10.5794545</v>
       </c>
       <c r="G3" t="n">
-        <v>12.8318665</v>
+        <v>15.423462</v>
       </c>
       <c r="H3" t="n">
-        <v>21.758159</v>
+        <v>22.535098</v>
       </c>
     </row>
     <row r="4">
@@ -532,19 +532,19 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>15.71901525384615</v>
+        <v>19.90887794230769</v>
       </c>
       <c r="E4" t="n">
-        <v>5.953345777396881</v>
+        <v>10.23679862625278</v>
       </c>
       <c r="F4" t="n">
-        <v>12.05703675</v>
+        <v>14.96553175</v>
       </c>
       <c r="G4" t="n">
-        <v>14.586399</v>
+        <v>17.2166325</v>
       </c>
       <c r="H4" t="n">
-        <v>17.2155825</v>
+        <v>21.118456</v>
       </c>
     </row>
   </sheetData>
@@ -616,19 +616,19 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>26590.10384615384</v>
+        <v>29371.56153846154</v>
       </c>
       <c r="E2" t="n">
-        <v>26477.42331537581</v>
+        <v>26532.28019619358</v>
       </c>
       <c r="F2" t="n">
-        <v>12267</v>
+        <v>15952.5</v>
       </c>
       <c r="G2" t="n">
-        <v>18598.5</v>
+        <v>20355</v>
       </c>
       <c r="H2" t="n">
-        <v>26650.25</v>
+        <v>28259</v>
       </c>
     </row>
     <row r="3">
@@ -644,19 +644,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>22608.22692307692</v>
+        <v>19349.09615384615</v>
       </c>
       <c r="E3" t="n">
-        <v>20323.77696212547</v>
+        <v>13598.54863232752</v>
       </c>
       <c r="F3" t="n">
-        <v>11083</v>
+        <v>11037</v>
       </c>
       <c r="G3" t="n">
-        <v>16978</v>
+        <v>15125</v>
       </c>
       <c r="H3" t="n">
-        <v>31034.75</v>
+        <v>29885.75</v>
       </c>
     </row>
     <row r="4">
@@ -672,19 +672,19 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>15592.28846153846</v>
+        <v>15551.75</v>
       </c>
       <c r="E4" t="n">
-        <v>333.1794498649276</v>
+        <v>1411.314645967645</v>
       </c>
       <c r="F4" t="n">
-        <v>15336</v>
+        <v>15393</v>
       </c>
       <c r="G4" t="n">
-        <v>15584.5</v>
+        <v>15665.5</v>
       </c>
       <c r="H4" t="n">
-        <v>15768.75</v>
+        <v>15846.5</v>
       </c>
     </row>
   </sheetData>
@@ -756,19 +756,19 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.780769230769231</v>
+        <v>5.026923076923077</v>
       </c>
       <c r="E2" t="n">
-        <v>1.735951716934651</v>
+        <v>1.747377006637779</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -784,10 +784,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.196153846153846</v>
+        <v>3.15</v>
       </c>
       <c r="E3" t="n">
-        <v>1.170744003034617</v>
+        <v>0.8033472445753427</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -896,19 +896,19 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>20.64230769230769</v>
+        <v>20.62307692307692</v>
       </c>
       <c r="E2" t="n">
-        <v>20.71443406028218</v>
+        <v>19.70526667917831</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -924,16 +924,16 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>21.44615384615384</v>
+        <v>23.48076923076923</v>
       </c>
       <c r="E3" t="n">
-        <v>21.89570277067626</v>
+        <v>20.79472236339014</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>18</v>
       </c>
       <c r="H3" t="n">
         <v>43</v>
@@ -952,16 +952,16 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>22.71153846153846</v>
+        <v>22.68076923076923</v>
       </c>
       <c r="E4" t="n">
-        <v>20.90310107830019</v>
+        <v>20.86512153579022</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="H4" t="n">
         <v>43</v>
@@ -1034,13 +1034,13 @@
         <v>260</v>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1076923076923077</v>
+        <v>0.1192307692307692</v>
       </c>
     </row>
     <row r="3">
@@ -1059,13 +1059,13 @@
         <v>260</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1038461538461539</v>
+        <v>0.03846153846153846</v>
       </c>
     </row>
     <row r="4">
@@ -1084,13 +1084,13 @@
         <v>260</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04230769230769231</v>
+        <v>0.02692307692307692</v>
       </c>
     </row>
   </sheetData>
@@ -1162,16 +1162,16 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E2" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -1190,19 +1190,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E3" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9069767441860465</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1221,16 +1221,16 @@
         <v>230</v>
       </c>
       <c r="E4" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8130434782608695</v>
+        <v>0.7913043478260869</v>
       </c>
     </row>
   </sheetData>

--- a/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
+++ b/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
@@ -1034,13 +1034,13 @@
         <v>260</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1192307692307692</v>
+        <v>0.08846153846153847</v>
       </c>
     </row>
     <row r="3">
@@ -1084,13 +1084,13 @@
         <v>260</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02692307692307692</v>
+        <v>0.01923076923076923</v>
       </c>
     </row>
   </sheetData>

--- a/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
+++ b/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
@@ -471,25 +471,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>29.15273405769231</v>
+        <v>29.66530070588235</v>
       </c>
       <c r="E2" t="n">
-        <v>18.68367103489186</v>
+        <v>19.63018942728218</v>
       </c>
       <c r="F2" t="n">
-        <v>17.14912675</v>
+        <v>16.546572</v>
       </c>
       <c r="G2" t="n">
-        <v>21.8696485</v>
+        <v>22.052884</v>
       </c>
       <c r="H2" t="n">
-        <v>33.2611755</v>
+        <v>35.096806</v>
       </c>
     </row>
     <row r="3">
@@ -499,25 +499,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>18.18594827692308</v>
+        <v>17.16152752156863</v>
       </c>
       <c r="E3" t="n">
-        <v>11.86179085453731</v>
+        <v>10.46118219543805</v>
       </c>
       <c r="F3" t="n">
-        <v>10.5794545</v>
+        <v>9.890757499999999</v>
       </c>
       <c r="G3" t="n">
-        <v>15.423462</v>
+        <v>13.838635</v>
       </c>
       <c r="H3" t="n">
-        <v>22.535098</v>
+        <v>21.4076285</v>
       </c>
     </row>
     <row r="4">
@@ -527,25 +527,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>19.90887794230769</v>
+        <v>12.9921065254902</v>
       </c>
       <c r="E4" t="n">
-        <v>10.23679862625278</v>
+        <v>5.726928110100146</v>
       </c>
       <c r="F4" t="n">
-        <v>14.96553175</v>
+        <v>9.2309185</v>
       </c>
       <c r="G4" t="n">
-        <v>17.2166325</v>
+        <v>11.989173</v>
       </c>
       <c r="H4" t="n">
-        <v>21.118456</v>
+        <v>14.5854025</v>
       </c>
     </row>
   </sheetData>
@@ -611,25 +611,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>29371.56153846154</v>
+        <v>32623.65882352941</v>
       </c>
       <c r="E2" t="n">
-        <v>26532.28019619358</v>
+        <v>29642.68116329046</v>
       </c>
       <c r="F2" t="n">
-        <v>15952.5</v>
+        <v>18357</v>
       </c>
       <c r="G2" t="n">
-        <v>20355</v>
+        <v>21049</v>
       </c>
       <c r="H2" t="n">
-        <v>28259</v>
+        <v>30831</v>
       </c>
     </row>
     <row r="3">
@@ -639,25 +639,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>19349.09615384615</v>
+        <v>14859.96078431373</v>
       </c>
       <c r="E3" t="n">
-        <v>13598.54863232752</v>
+        <v>12574.44937283347</v>
       </c>
       <c r="F3" t="n">
-        <v>11037</v>
+        <v>5897</v>
       </c>
       <c r="G3" t="n">
-        <v>15125</v>
+        <v>11932</v>
       </c>
       <c r="H3" t="n">
-        <v>29885.75</v>
+        <v>20392</v>
       </c>
     </row>
     <row r="4">
@@ -667,25 +667,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>15551.75</v>
+        <v>22327.76470588235</v>
       </c>
       <c r="E4" t="n">
-        <v>1411.314645967645</v>
+        <v>2466.967428012661</v>
       </c>
       <c r="F4" t="n">
-        <v>15393</v>
+        <v>20266</v>
       </c>
       <c r="G4" t="n">
-        <v>15665.5</v>
+        <v>20768</v>
       </c>
       <c r="H4" t="n">
-        <v>15846.5</v>
+        <v>24346</v>
       </c>
     </row>
   </sheetData>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.026923076923077</v>
+        <v>5.192156862745098</v>
       </c>
       <c r="E2" t="n">
-        <v>1.747377006637779</v>
+        <v>1.767582442725838</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -779,16 +779,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.15</v>
+        <v>3.192156862745098</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8033472445753427</v>
+        <v>0.8819812917059254</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -797,7 +797,7 @@
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>20.62307692307692</v>
+        <v>19.56470588235294</v>
       </c>
       <c r="E2" t="n">
-        <v>19.70526667917831</v>
+        <v>19.64133941430567</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -919,25 +919,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>23.48076923076923</v>
+        <v>23.67058823529412</v>
       </c>
       <c r="E3" t="n">
-        <v>20.79472236339014</v>
+        <v>21.58414493661361</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="4">
@@ -947,25 +947,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>22.68076923076923</v>
+        <v>22.67450980392157</v>
       </c>
       <c r="E4" t="n">
-        <v>20.86512153579022</v>
+        <v>19.91991686351409</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="H4" t="n">
-        <v>43</v>
+        <v>42.5</v>
       </c>
     </row>
   </sheetData>
@@ -1091,43 +1091,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E2" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F2" t="n">
-        <v>20.62307692307692</v>
+        <v>19.56470588235294</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>23.48076923076923</v>
+        <v>23.67058823529412</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.857692307692308</v>
+        <v>-4.105882352941176</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="M2" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="N2" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O2" t="n">
-        <v>4999.5</v>
+        <v>3438</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0002699733085314995</v>
+        <v>2.352585753319543e-09</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="b">
@@ -1151,43 +1151,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E3" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F3" t="n">
-        <v>20.62307692307692</v>
+        <v>19.56470588235294</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>22.68076923076923</v>
+        <v>22.67450980392157</v>
       </c>
       <c r="I3" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.057692307692307</v>
+        <v>-3.109803921568628</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="M3" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="N3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O3" t="n">
-        <v>6295.5</v>
+        <v>5059.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01094344756682542</v>
+        <v>0.0001794681604437926</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="b">
@@ -1211,43 +1211,43 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E4" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="F4" t="n">
-        <v>23.48076923076923</v>
+        <v>23.67058823529412</v>
       </c>
       <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22.67450980392157</v>
+      </c>
+      <c r="I4" t="n">
         <v>18</v>
       </c>
-      <c r="H4" t="n">
-        <v>22.68076923076923</v>
-      </c>
-      <c r="I4" t="n">
-        <v>15.5</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>0.996078431372549</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="M4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N4" t="n">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="O4" t="n">
-        <v>4041.5</v>
+        <v>1871</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01803759976477222</v>
+        <v>1.638907892178397e-05</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="b">
@@ -1271,43 +1271,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E5" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>29.15273405769231</v>
+        <v>29.66530070588235</v>
       </c>
       <c r="G5" t="n">
-        <v>21.8696485</v>
+        <v>22.052884</v>
       </c>
       <c r="H5" t="n">
-        <v>18.18594827692308</v>
+        <v>17.16152752156863</v>
       </c>
       <c r="I5" t="n">
-        <v>15.423462</v>
+        <v>13.838635</v>
       </c>
       <c r="J5" t="n">
-        <v>10.96678578076923</v>
+        <v>12.50377318431372</v>
       </c>
       <c r="K5" t="n">
-        <v>6.243156</v>
+        <v>6.230699999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M5" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>5963</v>
+        <v>4880</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24994583673498e-19</v>
+        <v>2.911567398945601e-22</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="b">
@@ -1331,43 +1331,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E6" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F6" t="n">
-        <v>29.15273405769231</v>
+        <v>29.66530070588235</v>
       </c>
       <c r="G6" t="n">
-        <v>21.8696485</v>
+        <v>22.052884</v>
       </c>
       <c r="H6" t="n">
-        <v>19.90887794230769</v>
+        <v>12.9921065254902</v>
       </c>
       <c r="I6" t="n">
-        <v>17.2166325</v>
+        <v>11.989173</v>
       </c>
       <c r="J6" t="n">
-        <v>9.243856115384615</v>
+        <v>16.67319418039216</v>
       </c>
       <c r="K6" t="n">
-        <v>4.013642499999999</v>
+        <v>8.817652999999998</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="M6" t="n">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8880</v>
+        <v>1261</v>
       </c>
       <c r="P6" t="n">
-        <v>2.713915276208933e-11</v>
+        <v>2.31307246376657e-37</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="b">
@@ -1391,43 +1391,43 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E7" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F7" t="n">
-        <v>18.18594827692308</v>
+        <v>17.16152752156863</v>
       </c>
       <c r="G7" t="n">
-        <v>15.423462</v>
+        <v>13.838635</v>
       </c>
       <c r="H7" t="n">
-        <v>19.90887794230769</v>
+        <v>12.9921065254902</v>
       </c>
       <c r="I7" t="n">
-        <v>17.2166325</v>
+        <v>11.989173</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.722929665384615</v>
+        <v>4.169420996078432</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.126105000000001</v>
+        <v>1.704666</v>
       </c>
       <c r="L7" t="n">
-        <v>178</v>
+        <v>75</v>
       </c>
       <c r="M7" t="n">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>11974</v>
+        <v>7685</v>
       </c>
       <c r="P7" t="n">
-        <v>3.920163412438003e-05</v>
+        <v>2.40109201857604e-13</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="b">
@@ -1451,43 +1451,43 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E8" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F8" t="n">
-        <v>5.026923076923077</v>
+        <v>5.192156862745098</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.192156862745098</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.876923076923077</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
         <v>223</v>
       </c>
       <c r="N8" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O8" t="n">
-        <v>38</v>
+        <v>331.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.689905852888567e-39</v>
+        <v>1.692352732633506e-38</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="b">
@@ -1511,13 +1511,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E9" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F9" t="n">
-        <v>5.026923076923077</v>
+        <v>5.192156862745098</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -1529,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>4.026923076923077</v>
+        <v>4.192156862745098</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.336270901406961e-45</v>
+        <v>9.839904367816287e-45</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="b">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E10" t="n">
         <v>250</v>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>3.192156862745098</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
@@ -1589,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.15</v>
+        <v>2.192156862745098</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1601,13 +1601,13 @@
         <v>250</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>6.66717709429488e-46</v>
+        <v>1.566658011559316e-46</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="b">
@@ -1631,43 +1631,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E11" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F11" t="n">
-        <v>29371.56153846154</v>
+        <v>32623.65882352941</v>
       </c>
       <c r="G11" t="n">
-        <v>20355</v>
+        <v>21049</v>
       </c>
       <c r="H11" t="n">
-        <v>19349.09615384615</v>
+        <v>14859.96078431373</v>
       </c>
       <c r="I11" t="n">
-        <v>15125</v>
+        <v>11932</v>
       </c>
       <c r="J11" t="n">
-        <v>10022.46538461539</v>
+        <v>17763.69803921569</v>
       </c>
       <c r="K11" t="n">
-        <v>5246</v>
+        <v>9557</v>
       </c>
       <c r="L11" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="M11" t="n">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>10406</v>
+        <v>5938</v>
       </c>
       <c r="P11" t="n">
-        <v>6.515609539108083e-08</v>
+        <v>1.294855781273659e-18</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="b">
@@ -1691,43 +1691,43 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E12" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F12" t="n">
-        <v>29371.56153846154</v>
+        <v>32623.65882352941</v>
       </c>
       <c r="G12" t="n">
-        <v>20355</v>
+        <v>21049</v>
       </c>
       <c r="H12" t="n">
-        <v>15551.75</v>
+        <v>22327.76470588235</v>
       </c>
       <c r="I12" t="n">
-        <v>15665.5</v>
+        <v>20768</v>
       </c>
       <c r="J12" t="n">
-        <v>13819.81153846154</v>
+        <v>10295.89411764706</v>
       </c>
       <c r="K12" t="n">
-        <v>4816.5</v>
+        <v>293</v>
       </c>
       <c r="L12" t="n">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="M12" t="n">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6061.5</v>
+        <v>13537</v>
       </c>
       <c r="P12" t="n">
-        <v>2.622173343761231e-19</v>
+        <v>0.01824614450543526</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="b">
@@ -1751,47 +1751,47 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E13" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F13" t="n">
-        <v>19349.09615384615</v>
+        <v>14859.96078431373</v>
       </c>
       <c r="G13" t="n">
-        <v>15125</v>
+        <v>11932</v>
       </c>
       <c r="H13" t="n">
-        <v>15551.75</v>
+        <v>22327.76470588235</v>
       </c>
       <c r="I13" t="n">
-        <v>15665.5</v>
+        <v>20768</v>
       </c>
       <c r="J13" t="n">
-        <v>3797.346153846154</v>
+        <v>-7467.803921568628</v>
       </c>
       <c r="K13" t="n">
-        <v>-571</v>
+        <v>-9099</v>
       </c>
       <c r="L13" t="n">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="M13" t="n">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>15104</v>
+        <v>5506</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1251920138473405</v>
+        <v>4.604000339103342e-20</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1852,22 +1852,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E2" t="n">
         <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08846153846153847</v>
+        <v>0.09019607843137255</v>
       </c>
     </row>
     <row r="3">
@@ -1877,22 +1877,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03846153846153846</v>
+        <v>0.03529411764705882</v>
       </c>
     </row>
     <row r="4">
@@ -1902,22 +1902,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01923076923076923</v>
+        <v>0.007843137254901961</v>
       </c>
     </row>
   </sheetData>
@@ -1983,25 +1983,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9949238578680203</v>
       </c>
     </row>
     <row r="3">
@@ -2011,22 +2011,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -2054,7 +2054,7 @@
         <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
         <v>0.7913043478260869</v>

--- a/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
+++ b/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
@@ -617,10 +617,10 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>32623.65882352941</v>
+        <v>32652.85098039216</v>
       </c>
       <c r="E2" t="n">
-        <v>29642.68116329046</v>
+        <v>29620.74192212403</v>
       </c>
       <c r="F2" t="n">
         <v>18357</v>
@@ -897,10 +897,10 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>19.56470588235294</v>
+        <v>19.61568627450981</v>
       </c>
       <c r="E2" t="n">
-        <v>19.64133941430567</v>
+        <v>19.67234932018046</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
         <v>170</v>
       </c>
       <c r="F2" t="n">
-        <v>19.56470588235294</v>
+        <v>19.61568627450981</v>
       </c>
       <c r="G2" t="n">
         <v>8</v>
@@ -1109,25 +1109,25 @@
         <v>14</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.105882352941176</v>
+        <v>-4.054901960784314</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N2" t="n">
         <v>85</v>
       </c>
       <c r="O2" t="n">
-        <v>3438</v>
+        <v>3552</v>
       </c>
       <c r="P2" t="n">
-        <v>2.352585753319543e-09</v>
+        <v>6.889580444546198e-09</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="b">
@@ -1157,7 +1157,7 @@
         <v>173</v>
       </c>
       <c r="F3" t="n">
-        <v>19.56470588235294</v>
+        <v>19.61568627450981</v>
       </c>
       <c r="G3" t="n">
         <v>8</v>
@@ -1169,7 +1169,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.109803921568628</v>
+        <v>-3.058823529411764</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
         <v>82</v>
       </c>
       <c r="O3" t="n">
-        <v>5059.5</v>
+        <v>5087</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001794681604437926</v>
+        <v>0.0002116835261952231</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="b">
@@ -1637,7 +1637,7 @@
         <v>255</v>
       </c>
       <c r="F11" t="n">
-        <v>32623.65882352941</v>
+        <v>32652.85098039216</v>
       </c>
       <c r="G11" t="n">
         <v>21049</v>
@@ -1649,7 +1649,7 @@
         <v>11932</v>
       </c>
       <c r="J11" t="n">
-        <v>17763.69803921569</v>
+        <v>17792.89019607843</v>
       </c>
       <c r="K11" t="n">
         <v>9557</v>
@@ -1664,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5938</v>
+        <v>5924</v>
       </c>
       <c r="P11" t="n">
-        <v>1.294855781273659e-18</v>
+        <v>1.164672968678729e-18</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="b">
@@ -1697,7 +1697,7 @@
         <v>255</v>
       </c>
       <c r="F12" t="n">
-        <v>32623.65882352941</v>
+        <v>32652.85098039216</v>
       </c>
       <c r="G12" t="n">
         <v>21049</v>
@@ -1709,7 +1709,7 @@
         <v>20768</v>
       </c>
       <c r="J12" t="n">
-        <v>10295.89411764706</v>
+        <v>10325.0862745098</v>
       </c>
       <c r="K12" t="n">
         <v>293</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>13537</v>
+        <v>13513</v>
       </c>
       <c r="P12" t="n">
-        <v>0.01824614450543526</v>
+        <v>0.01726842986840734</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="b">
@@ -1861,13 +1861,13 @@
         <v>255</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09019607843137255</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -1992,16 +1992,16 @@
         <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9949238578680203</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">

--- a/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
+++ b/out/RQ2_architecture_metrics/RQ2_architecture_metrics.xlsx
@@ -12,8 +12,9 @@
     <sheet name="llm_calls" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="code_lines" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="pairwise_wilcoxon" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="fallback" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="yaml_validity" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="pairwise_a12" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="fallback" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="yaml_validity" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1547,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>9.839904367816287e-45</v>
+        <v>9.839904367816289e-45</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="b">
@@ -1787,7 +1788,7 @@
         <v>5506</v>
       </c>
       <c r="P13" t="n">
-        <v>4.604000339103342e-20</v>
+        <v>4.604000339103341e-20</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="b">
@@ -1805,43 +1806,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>arch_id</t>
+          <t>arch_a</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_responses</t>
+          <t>arch_b</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_runs</t>
+          <t>metric</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>fallback_observed_n</t>
+          <t>a12_arch_a_over_arch_b</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>fallback_count</t>
+          <t>a12_arch_b_over_arch_a</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>non_fallback_count</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>fallback_rate</t>
+          <t>a12_magnitude</t>
         </is>
       </c>
     </row>
@@ -1851,73 +1847,334 @@
           <t>agentic_architecture</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>255</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>answer_code_lines</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>255</v>
+        <v>0.445282583621684</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F2" t="n">
-        <v>238</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.554717416378316</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>graph_based_architecture</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>255</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>answer_code_lines</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>255</v>
+        <v>0.4501653210303729</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F3" t="n">
-        <v>246</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.03529411764705882</v>
+        <v>0.5498346789696271</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>one_node_architecture</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>255</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>answer_code_lines</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>255</v>
+        <v>0.5116878123798539</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>253</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.007843137254901961</v>
+        <v>0.4883121876201461</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>latency_s</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7459284890426759</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2540715109573241</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>latency_s</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8707881584006152</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1292118415993848</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>latency_s</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6204998077662438</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3795001922337562</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>llm_call_count</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8772933487120338</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1227066512879662</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>llm_call_count</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>llm_call_count</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9901960784313726</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.009803921568627416</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>total_input_tokens</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7771318723567858</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2228681276432142</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>total_input_tokens</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5470972702806612</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4529027297193388</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>total_input_tokens</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1845444059976932</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8154555940023068</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1931,6 +2188,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arch_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_responses</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_runs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fallback_observed_n</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fallback_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>non_fallback_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fallback_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>agentic_architecture</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>255</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>255</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2" t="n">
+        <v>238</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>graph_based_architecture</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>255</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>255</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>246</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03529411764705882</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>one_node_architecture</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>255</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>255</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>253</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.007843137254901961</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
